--- a/AAII_Financials/Quarterly/ALVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALVR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/ALVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
   <si>
     <t>ALVR</t>
   </si>
@@ -656,101 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -760,8 +761,14 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -792,17 +799,17 @@
       <c r="L8" s="3">
         <v>0</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -811,17 +818,17 @@
         <v>0</v>
       </c>
       <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>200</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,8 +838,14 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -902,8 +915,14 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -973,8 +992,14 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,68 +1025,70 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>33400</v>
+      </c>
+      <c r="F12" s="3">
         <v>34200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>34800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>30700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>28400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>30000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>31400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>29100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>41600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>33100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>25700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>20400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>16800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>17200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>8900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>6800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>16200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>1200</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1071,8 +1098,14 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,31 +1175,37 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>18600</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1213,8 +1252,14 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1284,8 +1329,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,68 +1359,70 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>62400</v>
+      </c>
+      <c r="F17" s="3">
         <v>47000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>47300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>43200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>40400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>43000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>44600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>43200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>55800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>45500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>37700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>30900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>25400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>23900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>12200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>9800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>26900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2900</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1379,8 +1432,14 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1388,59 +1447,59 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-62400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="G18" s="3">
         <v>-47300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-43200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-40400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-43000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-44600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-43200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-55800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-45500</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-25400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-12200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-9800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-26700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2700</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1450,8 +1509,14 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,8 +1542,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1486,59 +1553,59 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>2800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,8 +1615,14 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1557,59 +1630,59 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-59700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-44200</v>
+      </c>
+      <c r="G21" s="3">
         <v>-45200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-41100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-38500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-42000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-44400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-43400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-56800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-45500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-25200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-11600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-9300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-23800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-2500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,8 +1692,14 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1690,68 +1769,74 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-59800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-44300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-45300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-41200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-38600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-42100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-44500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-43900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-56900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-45500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-37600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-30900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-25200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-11600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-9300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-23800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1761,41 +1846,47 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,11 +1899,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1832,8 +1923,14 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,68 +2000,74 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-59700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-44300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-45300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-41200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-38100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-42100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-44600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-43900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-57900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-45500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-37600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-30900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-25200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-11600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-9300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-23800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1974,68 +2077,74 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-59700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-44300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-45300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-41200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-38100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-42100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-44600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-43900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-57900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-45500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-37600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-30900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-25200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-11600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-9300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-23800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2045,8 +2154,14 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2231,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2308,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2385,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,8 +2462,14 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2338,59 +2477,59 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-2800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2400,68 +2539,74 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-59700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-44300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-45300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-41200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-38100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-42100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-44600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-43900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-57900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-45500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-37600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-30900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-25200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-11600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-9300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-23800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,8 +2616,14 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,68 +2693,74 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-59700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-44300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-45300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-41200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-38100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-42100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-44600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-43900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-57900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-45500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-37600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-30900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-25200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-11600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-9300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-23800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2613,73 +2770,79 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2689,8 +2852,14 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2885,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,62 +2914,64 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>90100</v>
+      </c>
+      <c r="F41" s="3">
         <v>95600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>197000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>115700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>106100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>123800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>71100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>100200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>201700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>243200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>225400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>168600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>122700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>142300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>78300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>64400</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,62 +2987,68 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>93800</v>
+      </c>
+      <c r="F42" s="3">
         <v>117700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>49600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>86900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>127700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>140300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>101600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>101200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>46500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>32700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>87900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>168300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>233700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>236200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>26200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>51400</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2885,8 +3064,14 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2894,22 +3079,22 @@
         <v>200</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F43" s="3">
         <v>200</v>
       </c>
       <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>200</v>
+      </c>
+      <c r="J43" s="3">
         <v>300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>200</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -2918,29 +3103,29 @@
         <v>200</v>
       </c>
       <c r="M43" s="3">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3">
+        <v>200</v>
+      </c>
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>700</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,8 +3141,14 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3027,62 +3218,68 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F45" s="3">
         <v>6500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>9500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>9100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>7700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>5200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>4500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>4900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,62 +3295,68 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>141500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>187600</v>
+      </c>
+      <c r="F46" s="3">
         <v>220000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>252900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>212300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>243100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>272000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>176500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>206400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>253300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>281900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>316000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>339700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>361300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>383900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>107300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>117400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3372,14 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3240,62 +3449,68 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F48" s="3">
         <v>26000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>28200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>30400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>32600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>20100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>21800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>22800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>31300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>32600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>10800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>11600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>9500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>9800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>10600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>11300</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,8 +3526,14 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3382,8 +3603,14 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3680,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,47 +3757,53 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1300</v>
       </c>
       <c r="G52" s="3">
         <v>1500</v>
       </c>
       <c r="H52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J52" s="3">
         <v>1600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>700</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3577,11 +3816,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3595,8 +3834,14 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,62 +3911,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>144100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>190800</v>
+      </c>
+      <c r="F54" s="3">
         <v>248300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>282700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>244000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>277100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>293700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>200000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>231100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>286600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>316500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>327500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>351300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>370800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>393700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>117800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>128700</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3988,14 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +4021,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,61 +4050,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>5200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>8400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>700</v>
       </c>
       <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>700</v>
+      </c>
+      <c r="T57" s="3">
+        <v>1800</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
@@ -3862,8 +4123,14 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3933,62 +4200,68 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>21600</v>
+      </c>
+      <c r="F59" s="3">
         <v>29100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>25400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>20800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>21300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>15800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>16100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>14200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>29500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>24000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>16500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>13400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>11300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>11700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>8200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>5900</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,62 +4277,68 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>28400</v>
+      </c>
+      <c r="F60" s="3">
         <v>33100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>30600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>25000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>24300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>20700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>21600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>18600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>37900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>24200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>20700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>15500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>12300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>13500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>8900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>7700</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,8 +4354,14 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4146,62 +4431,68 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F62" s="3">
         <v>19900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>23000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>25600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>28200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>19800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>20300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>20800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>23500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>25100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>5400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>5500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>6300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>7100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>7900</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4508,14 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4585,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4662,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,62 +4739,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>45000</v>
+      </c>
+      <c r="F66" s="3">
         <v>53000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>53600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>50500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>52600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>40500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>41900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>39400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>61300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>49200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>25000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>20900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>17800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>19800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>16000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>15600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4816,14 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4849,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4922,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4999,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4715,17 +5050,17 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>173100</v>
       </c>
-      <c r="R70" s="3">
+      <c r="T70" s="3">
         <v>173100</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4741,8 +5076,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,62 +5153,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-686500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-656200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-596500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-552200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-507000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-465800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-427600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-385600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-340900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-297100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-239100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-193600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-156000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-125100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-99900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-76300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-64700</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5230,14 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5307,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5384,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,62 +5461,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>120400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>145800</v>
+      </c>
+      <c r="F76" s="3">
         <v>195300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>229100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>193500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>224500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>253200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>158100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>191700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>225300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>267300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>302500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>330400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>353100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>373900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-71300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-60000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5538,14 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,73 +5615,79 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5314,68 +5697,74 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-59700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-44300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-45300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-41200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-38100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-42100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-44600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-43900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-57900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-45500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-37600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-30900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-25200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-11600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-9300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-23800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5385,8 +5774,14 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,13 +5807,15 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -5436,16 +5833,16 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -5468,11 +5865,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5483,8 +5880,14 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5957,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +6034,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +6111,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +6188,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,68 +6265,74 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-34500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-27100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-32100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-31600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-35100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-28900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-46500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-28100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-36400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-22900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-18900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-21100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-11100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-10500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-20200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-2000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6342,14 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,8 +6375,10 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5963,7 +6404,7 @@
         <v>-300</v>
       </c>
       <c r="K91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-300</v>
@@ -5972,29 +6413,29 @@
         <v>-300</v>
       </c>
       <c r="N91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6007,8 +6448,14 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6525,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,67 +6602,73 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>25200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-66900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>37900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>41700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>13500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-38600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-55000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-13500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>55000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>79700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>64800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-210300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>25000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>13800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-64600</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6220,8 +6679,14 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6712,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6318,8 +6785,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6862,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6939,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,67 +7016,73 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>126400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>292300</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>120900</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
@@ -6602,8 +7093,14 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6632,23 +7129,23 @@
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6661,11 +7158,11 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -6673,68 +7170,74 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-101300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>81300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>9600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-17700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>52700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-29100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-101500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-41500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>18600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>56800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>46000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-19600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>64000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>13900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>3300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>36100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6742,6 +7245,12 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
   <si>
     <t>ALVR</t>
   </si>
@@ -656,105 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,8 +768,11 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -805,14 +809,14 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
+      <c r="O8" s="3">
+        <v>0</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -824,13 +828,13 @@
         <v>0</v>
       </c>
       <c r="U8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
         <v>200</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
+      <c r="W8" s="3">
+        <v>200</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
@@ -844,8 +848,11 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -921,8 +928,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -998,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,71 +1040,72 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
         <v>12200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>34200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>34800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>30700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>28400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>30000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>31400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>41600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>33100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>20400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>17200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>16200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1200</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1118,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,20 +1198,23 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>500</v>
+      </c>
+      <c r="E14" s="3">
         <v>9500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>18600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1207,8 +1227,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1258,8 +1278,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1335,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,71 +1387,72 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E17" s="3">
         <v>32300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>62400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>47000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>47300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>43200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>40400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>43000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>44600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>55800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>45500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>30900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>26900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2900</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,8 +1465,11 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1447,62 +1477,62 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-62400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-47000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-47300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-43200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-40400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-43000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-44600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-43200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-55800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-45500</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>-25400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-23900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-12200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-26700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2700</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1515,8 +1545,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,8 +1577,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1553,62 +1587,62 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>2000</v>
       </c>
       <c r="H20" s="3">
         <v>2000</v>
       </c>
       <c r="I20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J20" s="3">
         <v>1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
-      </c>
-      <c r="S20" s="3">
-        <v>500</v>
       </c>
       <c r="T20" s="3">
         <v>500</v>
       </c>
       <c r="U20" s="3">
+        <v>500</v>
+      </c>
+      <c r="V20" s="3">
         <v>2800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,8 +1655,11 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1630,62 +1667,62 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-59700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-44200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-45200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-41100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-38500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-42000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-44400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-43400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-56800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-45500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-25200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-23600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-11600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-23800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2500</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,8 +1735,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1775,71 +1815,74 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-30300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-59800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-44300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-45300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-41200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-38600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-42100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-44500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-43900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-56900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-45500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-37600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-25200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-23600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-23800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1852,20 +1895,23 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1873,23 +1919,23 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1905,8 +1951,8 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1929,8 +1975,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,71 +2055,74 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-30300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-59700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-44300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-45300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-41200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-42100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-44600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-43900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-57900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-45500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-37600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-25200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-23600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-23800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2083,71 +2135,74 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-30300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-59700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-44300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-45300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-41200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-42100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-44600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-43900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-57900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-45500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-37600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-25200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-23600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-23800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2500</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2160,8 +2215,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,8 +2535,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2477,62 +2547,62 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-2000</v>
       </c>
       <c r="H32" s="3">
         <v>-2000</v>
       </c>
       <c r="I32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-500</v>
       </c>
       <c r="T32" s="3">
         <v>-500</v>
       </c>
       <c r="U32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V32" s="3">
         <v>-2800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,71 +2615,74 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-30300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-59700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-44300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-45300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-41200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-42100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-44600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-43900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-57900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-45500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-37600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-25200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-23600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-23800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2500</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2622,8 +2695,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,71 +2775,74 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-30300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-59700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-44300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-45300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-41200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-42100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-44600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-43900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-57900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-45500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-37600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-25200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-23600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-23800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2500</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2776,76 +2855,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2940,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,65 +3002,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>104700</v>
+      </c>
+      <c r="E41" s="3">
         <v>86000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>90100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>95600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>197000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>115700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>106100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>123800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>71100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>201700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>243200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>225400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>168600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>122700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>142300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>78300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>64400</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2993,65 +3080,68 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E42" s="3">
         <v>54500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>93800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>117700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>49600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>86900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>127700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>140300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>101600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>101200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>46500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>32700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>87900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>168300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>233700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>236200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>26200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>51400</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3070,13 +3160,16 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
@@ -3085,50 +3178,50 @@
         <v>200</v>
       </c>
       <c r="G43" s="3">
+        <v>200</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
-      </c>
-      <c r="H43" s="3">
-        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
       </c>
       <c r="J43" s="3">
+        <v>200</v>
+      </c>
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>400</v>
-      </c>
-      <c r="P43" s="3">
-        <v>500</v>
       </c>
       <c r="Q43" s="3">
         <v>500</v>
       </c>
       <c r="R43" s="3">
+        <v>500</v>
+      </c>
+      <c r="S43" s="3">
         <v>600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>700</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3147,8 +3240,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3224,65 +3320,68 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1000</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3301,65 +3400,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>129900</v>
+      </c>
+      <c r="E46" s="3">
         <v>141500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>187600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>220000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>252900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>212300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>243100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>272000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>176500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>206400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>253300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>281900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>316000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>339700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>361300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>383900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>107300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>117400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3455,65 +3560,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11300</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,8 +3640,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3609,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,8 +3880,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3772,41 +3892,41 @@
         <v>600</v>
       </c>
       <c r="E52" s="3">
+        <v>600</v>
+      </c>
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3822,8 +3942,8 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3840,8 +3960,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,65 +4040,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E54" s="3">
         <v>144100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>190800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>248300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>282700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>244000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>277100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>293700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>200000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>231100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>286600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>316500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>327500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>351300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>370800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>393700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>117800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>128700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,65 +4182,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4129,8 +4260,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4206,65 +4340,68 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E59" s="3">
         <v>6900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>29500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5900</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,65 +4420,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E60" s="3">
         <v>7700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>37900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>24200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7700</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4360,8 +4500,11 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4437,65 +4580,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E62" s="3">
         <v>16000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>19900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>28200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>19800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7900</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4514,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,65 +4900,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E66" s="3">
         <v>23700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>40500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>41900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>61300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>49200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5056,13 +5224,13 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>173100</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>173100</v>
       </c>
       <c r="U70" s="3">
-        <v>0</v>
+        <v>173100</v>
       </c>
       <c r="V70" s="3">
         <v>0</v>
@@ -5082,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,65 +5330,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-692600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-686500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-656200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-596500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-552200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-507000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-465800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-427600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-385600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-340900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-297100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-239100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-193600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-156000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-125100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-99900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-76300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-64700</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5236,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,65 +5650,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>120300</v>
+      </c>
+      <c r="E76" s="3">
         <v>120400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>145800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>195300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>229100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>193500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>224500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>253200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>158100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>191700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>225300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>267300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>302500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>330400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>353100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>373900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-71300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-60000</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5544,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,76 +5810,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,71 +5895,74 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-30300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-59700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-44300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-45300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-41200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-42100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-44600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-43900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-57900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-45500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-37600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-25200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-23600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-23800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2500</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5780,8 +5975,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,8 +6007,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5818,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -5839,14 +6038,14 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -5871,8 +6070,8 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -5886,8 +6085,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,71 +6485,74 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-44400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-30700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-34500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-32100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-31600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-35100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-46500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-28100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-36400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-22900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-20200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2000</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6348,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,8 +6597,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6404,10 +6625,10 @@
         <v>-300</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="L91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-300</v>
@@ -6419,11 +6640,11 @@
         <v>-300</v>
       </c>
       <c r="P91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6433,12 +6654,12 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6454,8 +6675,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,70 +6835,73 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E94" s="3">
         <v>40000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>25200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-66900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>37900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>41700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>13500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-38600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-55000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>55000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>79700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>64800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-210300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>25000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>13800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-64600</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
@@ -6685,8 +6915,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6791,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,70 +7265,73 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+      <c r="G100" s="3">
+        <v>0</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>126400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>292300</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>120900</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
@@ -7099,8 +7345,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7135,20 +7384,20 @@
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7164,8 +7413,8 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -7176,71 +7425,74 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-101300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>81300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>52700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-29100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-101500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-41500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>56800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>46000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-19600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>64000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>13900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>36100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7251,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALVR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALVR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="92">
   <si>
     <t>ALVR</t>
   </si>
@@ -656,109 +656,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -771,31 +772,34 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -812,14 +816,14 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
+      <c r="P8" s="3">
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -831,13 +835,13 @@
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3">
         <v>200</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
+      <c r="X8" s="3">
+        <v>200</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
@@ -851,8 +855,11 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -931,8 +938,11 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1011,8 +1021,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,74 +1054,75 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>34200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>34800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>28400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>30000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>31400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>41600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>33100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>16800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>17200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>16200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1200</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,8 +1135,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,22 +1218,25 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3">
-        <v>9500</v>
-      </c>
       <c r="F14" s="3">
-        <v>18600</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>8700</v>
+      </c>
+      <c r="G14" s="3">
+        <v>17400</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1224,14 +1244,14 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>-700</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1281,31 +1301,34 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1361,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1388,74 +1414,75 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7800</v>
+        <v>5600</v>
       </c>
       <c r="E17" s="3">
-        <v>32300</v>
+        <v>7300</v>
       </c>
       <c r="F17" s="3">
-        <v>62400</v>
+        <v>22800</v>
       </c>
       <c r="G17" s="3">
+        <v>43800</v>
+      </c>
+      <c r="H17" s="3">
         <v>47000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>47300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>43200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>40400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>44600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>45500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>30900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>26900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2900</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1468,74 +1495,77 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-5600</v>
       </c>
       <c r="E18" s="3">
-        <v>-32300</v>
+        <v>-7300</v>
       </c>
       <c r="F18" s="3">
-        <v>-62400</v>
+        <v>-22800</v>
       </c>
       <c r="G18" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="H18" s="3">
         <v>-47000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-47300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-43200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-40400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-43000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-44600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-43200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-55800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-45500</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-25400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-23900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-12200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-26700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2700</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,8 +1578,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,74 +1611,75 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>2000</v>
+        <v>-300</v>
       </c>
       <c r="F20" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>2000</v>
+        <v>-1200</v>
       </c>
       <c r="I20" s="3">
-        <v>2000</v>
+        <v>-500</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
-      </c>
-      <c r="T20" s="3">
-        <v>500</v>
       </c>
       <c r="U20" s="3">
         <v>500</v>
       </c>
       <c r="V20" s="3">
+        <v>500</v>
+      </c>
+      <c r="W20" s="3">
         <v>2800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,74 +1692,77 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-5400</v>
       </c>
       <c r="E21" s="3">
-        <v>-30300</v>
+        <v>-6800</v>
       </c>
       <c r="F21" s="3">
-        <v>-59700</v>
+        <v>-22700</v>
       </c>
       <c r="G21" s="3">
-        <v>-44200</v>
+        <v>-43700</v>
       </c>
       <c r="H21" s="3">
-        <v>-45200</v>
+        <v>-45700</v>
       </c>
       <c r="I21" s="3">
-        <v>-41100</v>
+        <v>-46700</v>
       </c>
       <c r="J21" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="K21" s="3">
         <v>-38500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-42000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-44400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-43400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-56800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-45500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-25200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-23600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-11600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-23800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2500</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,31 +1775,34 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1818,74 +1858,77 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-30300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-59800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-44300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-45300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-41200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-38600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-42100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-44500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-43900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-56900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-45500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-30900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-25200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-23800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1898,8 +1941,11 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1909,36 +1955,36 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1954,8 +2000,8 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1978,8 +2024,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,74 +2107,77 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-30300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-59700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-44300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-45300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-41200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-38100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-42100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-44600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-43900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-57900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-45500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-25200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-23800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2138,74 +2190,77 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-30300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-59700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-44300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-45300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-41200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-38100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-42100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-44600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-43900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-57900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-45500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-25200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-23600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-23800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2218,8 +2273,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2298,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2378,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2458,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2538,74 +2605,77 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>-2000</v>
+        <v>300</v>
       </c>
       <c r="F32" s="3">
-        <v>-2600</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-2700</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-2000</v>
+        <v>1200</v>
       </c>
       <c r="I32" s="3">
-        <v>-2000</v>
+        <v>500</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-500</v>
       </c>
       <c r="U32" s="3">
         <v>-500</v>
       </c>
       <c r="V32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W32" s="3">
         <v>-2800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2618,74 +2688,77 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-30300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-59700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-44300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-45300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-41200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-38100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-42100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-44600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-43900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-57900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-45500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-25200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-23800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2698,8 +2771,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2778,74 +2854,77 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-30300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-59700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-44300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-45300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-41200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-38100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-42100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-44600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-43900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-57900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-45500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-25200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-23800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,79 +2937,82 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2943,8 +3025,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2973,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3003,68 +3089,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>116900</v>
+      </c>
+      <c r="E41" s="3">
         <v>104700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>86000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>90100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>95600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>197000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>115700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>106100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>123800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>71100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>201700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>243200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>225400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>168600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>122700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>142300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>78300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>64400</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,68 +3170,71 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E42" s="3">
         <v>24900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>54500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>93800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>117700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>49600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>86900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>127700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>140300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>101600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>101200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>46500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>32700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>87900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>168300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>233700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>236200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>26200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>51400</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3163,8 +3253,11 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3172,7 +3265,7 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>200</v>
@@ -3181,50 +3274,50 @@
         <v>200</v>
       </c>
       <c r="H43" s="3">
+        <v>200</v>
+      </c>
+      <c r="I43" s="3">
         <v>100</v>
-      </c>
-      <c r="I43" s="3">
-        <v>200</v>
       </c>
       <c r="J43" s="3">
         <v>200</v>
       </c>
       <c r="K43" s="3">
+        <v>200</v>
+      </c>
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>500</v>
       </c>
       <c r="R43" s="3">
         <v>500</v>
       </c>
       <c r="S43" s="3">
+        <v>500</v>
+      </c>
+      <c r="T43" s="3">
         <v>600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>700</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3243,31 +3336,34 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3323,68 +3419,71 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>6500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>6300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>9500</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>9100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1000</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3403,68 +3502,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E46" s="3">
         <v>129900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>141500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>187600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>220000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>252900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>212300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>243100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>272000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>176500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>206400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>253300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>281900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>316000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>339700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>361300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>383900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>107300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>117400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,31 +3585,34 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3563,68 +3668,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3">
         <v>500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>30400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>31300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11300</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,8 +3751,11 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3723,8 +3834,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3803,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,53 +4000,56 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>600</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3">
         <v>600</v>
       </c>
       <c r="F52" s="3">
+        <v>600</v>
+      </c>
+      <c r="G52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3945,8 +4065,8 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -3963,8 +4083,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4043,68 +4166,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E54" s="3">
         <v>131000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>144100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>190800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>248300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>282700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>244000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>277100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>293700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>200000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>231100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>286600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>316500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>327500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>351300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>370800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>393700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>117800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>128700</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4153,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4183,8 +4313,9 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4192,59 +4323,59 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1800</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4263,8 +4394,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4272,22 +4406,22 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4343,68 +4477,71 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>2200</v>
-      </c>
-      <c r="E59" s="3">
-        <v>6900</v>
-      </c>
-      <c r="F59" s="3">
-        <v>21600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>29100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>25400</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I59" s="3">
-        <v>20800</v>
+        <v>100</v>
       </c>
       <c r="J59" s="3">
+        <v>100</v>
+      </c>
+      <c r="K59" s="3">
         <v>21300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>29500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,68 +4560,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>24300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>37900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>24200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>20700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7700</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,8 +4643,11 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4512,22 +4655,22 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>16600</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>25600</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4583,68 +4726,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>8300</v>
-      </c>
-      <c r="E62" s="3">
-        <v>16000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>16600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>19900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>23000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>25600</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>28200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>25100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7900</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4809,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4743,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4823,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4903,68 +5058,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E66" s="3">
         <v>10700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>50500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>40500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>41900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>61300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>49200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>19800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15600</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5013,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5093,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5173,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5227,13 +5395,13 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>173100</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>173100</v>
       </c>
       <c r="V70" s="3">
-        <v>0</v>
+        <v>173100</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -5253,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5333,68 +5504,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-696700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-692600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-686500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-656200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-596500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-552200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-507000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-465800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-427600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-385600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-340900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-297100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-239100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-193600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-156000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-125100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-99900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-76300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-64700</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5413,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5493,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5573,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5653,68 +5836,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>121100</v>
+      </c>
+      <c r="E76" s="3">
         <v>120300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>120400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>145800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>195300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>229100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>193500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>224500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>253200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>158100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>191700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>225300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>267300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>302500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>330400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>353100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>373900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-71300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-60000</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5733,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5813,79 +6002,82 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5898,74 +6090,77 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-30300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-59700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-44300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-45300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-41200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-38100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-42100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-44600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-43900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-57900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-45500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-25200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-23800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,8 +6173,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6008,16 +6206,17 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -6032,7 +6231,7 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -6041,14 +6240,14 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
+        <v>100</v>
+      </c>
+      <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -6073,8 +6272,8 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
@@ -6088,8 +6287,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6168,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6248,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6328,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6408,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6488,74 +6702,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-44400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-30700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-34500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-27100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-32100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-31600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-35100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-28900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-46500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-36400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-22900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-21100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-18100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-10500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-20200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2000</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6568,8 +6785,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6598,40 +6818,41 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="M91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
@@ -6643,11 +6864,11 @@
         <v>-300</v>
       </c>
       <c r="Q91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6657,12 +6878,12 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6678,8 +6899,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6758,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6838,73 +7065,76 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E94" s="3">
         <v>30000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>40000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>25200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-66900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>37900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>41700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>13500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-38600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-55000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>55000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>79700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>64800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-210300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>25000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>13800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-64600</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
@@ -6918,8 +7148,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6948,31 +7181,32 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7028,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7108,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7188,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7268,73 +7511,76 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>70500</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>126400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>292300</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>120900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
+      <c r="X100" s="3">
+        <v>0</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
@@ -7348,31 +7594,34 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7387,20 +7636,20 @@
         <v>0</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7416,8 +7665,8 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7428,74 +7677,77 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E102" s="3">
         <v>18700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-101300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>81300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>52700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-29100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-101500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-41500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>18600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>56800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>46000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-19600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>64000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>36100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2000</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7506,6 +7758,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
